--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1987,6 +1987,3785 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129472103</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628614</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6955785</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>200 ex</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129472072</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628696</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6955790</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129472100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>628692</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6955809</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129472086</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628666</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6955777</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129472088</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628599</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6955803</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129464348</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628653</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6955846</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129472096</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628688</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6955783</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129472094</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628694</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6955797</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129472079</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628550</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6955726</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129472068</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628531</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6955789</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129472092</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628592</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6955801</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129472097</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628701</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6955786</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129472089</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628636</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6955724</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129472095</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97581</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628650</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6955757</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129472065</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>628619</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6955754</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129472091</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>628624</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6955759</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129472101</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>628571</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6955635</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129464211</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>628639</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6955882</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129472075</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>628611</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6955783</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129472106</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>628696</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6955801</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>40 ex</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129472067</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>628597</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6955801</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129472080</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>628556</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6955681</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129472085</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>628557</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6955601</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129472083</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>628567</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6955620</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129472066</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>628619</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6955769</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129472099</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>628699</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6955804</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129472102</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>628568</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6955839</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40 ex</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129472105</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>628512</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6955747</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129472084</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>628556</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6955608</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129473075</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>48</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>628595</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6955801</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129472109</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>628566</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6955643</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129472087</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>628620</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6955761</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129472077</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>628513</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6955744</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129472076</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>628542</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6955835</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129472108</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>628517</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6955756</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129472073</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>628698</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6955800</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129472069</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>628725</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6955752</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129472082</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>628544</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6955659</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472103</v>
+        <v>129472086</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628614</v>
+        <v>628666</v>
       </c>
       <c r="R14" t="n">
-        <v>6955785</v>
+        <v>6955777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R16" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472086</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628666</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955777</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129472096</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472079</v>
+        <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628550</v>
+        <v>628694</v>
       </c>
       <c r="R22" t="n">
-        <v>6955726</v>
+        <v>6955797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,11 +2856,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R23" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2953,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472095</v>
       </c>
       <c r="B26" t="n">
-        <v>91841</v>
+        <v>97583</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628650</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472095</v>
+        <v>129472089</v>
       </c>
       <c r="B27" t="n">
-        <v>97581</v>
+        <v>91843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628650</v>
+        <v>628636</v>
       </c>
       <c r="R27" t="n">
-        <v>6955757</v>
+        <v>6955724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472091</v>
       </c>
       <c r="B28" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472091</v>
+        <v>129472065</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628624</v>
+        <v>628619</v>
       </c>
       <c r="R29" t="n">
-        <v>6955759</v>
+        <v>6955754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,50 +3662,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R31" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3737,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3871,32 +3866,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3906,7 +3901,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R33" t="n">
         <v>6955801</v>
@@ -3942,11 +3937,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B34" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,34 +3974,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472080</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628556</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955681</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472085</v>
+        <v>129472080</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628557</v>
+        <v>628556</v>
       </c>
       <c r="R36" t="n">
-        <v>6955601</v>
+        <v>6955681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472105</v>
+        <v>129472084</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628512</v>
+        <v>628556</v>
       </c>
       <c r="R41" t="n">
-        <v>6955747</v>
+        <v>6955608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,32 +4774,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R42" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4879,7 +4879,7 @@
         <v>129473075</v>
       </c>
       <c r="B43" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>129472109</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,6 +5446,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5475,7 +5480,7 @@
         <v>129472073</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5572,7 +5577,7 @@
         <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5666,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R51" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472086</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628666</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955777</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2060,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472100</v>
+        <v>129472103</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628692</v>
+        <v>628614</v>
       </c>
       <c r="R15" t="n">
-        <v>6955809</v>
+        <v>6955785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R16" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472103</v>
+        <v>129472086</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628614</v>
+        <v>628666</v>
       </c>
       <c r="R17" t="n">
-        <v>6955785</v>
+        <v>6955777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472095</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
-        <v>97583</v>
+        <v>91847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628650</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955757</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472089</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628636</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955724</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472091</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955759</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472065</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>97587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628619</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955754</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,45 +3662,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R31" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,7 +3742,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3874,7 @@
         <v>129472067</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,50 +3968,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R35" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R37" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R41" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>91762</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4785,34 +4785,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R42" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,17 +4850,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4876,48 +4875,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129473075</v>
+        <v>129472084</v>
       </c>
       <c r="B43" t="n">
-        <v>91758</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628595</v>
+        <v>628556</v>
       </c>
       <c r="R43" t="n">
-        <v>6955801</v>
+        <v>6955608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,13 +4948,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R48" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,11 +5446,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5480,7 +5475,7 @@
         <v>129472073</v>
       </c>
       <c r="B49" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5577,7 +5572,7 @@
         <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R51" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472103</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628614</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955785</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,11 +2157,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472100</v>
+        <v>129472103</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628692</v>
+        <v>628614</v>
       </c>
       <c r="R16" t="n">
-        <v>6955809</v>
+        <v>6955785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B21" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R21" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R22" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472079</v>
+        <v>129472094</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628550</v>
+        <v>628694</v>
       </c>
       <c r="R23" t="n">
-        <v>6955726</v>
+        <v>6955797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,11 +2958,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472097</v>
+        <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628701</v>
+        <v>628636</v>
       </c>
       <c r="R25" t="n">
-        <v>6955786</v>
+        <v>6955724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628624</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472091</v>
+        <v>129472095</v>
       </c>
       <c r="B27" t="n">
-        <v>91847</v>
+        <v>97595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628624</v>
+        <v>628650</v>
       </c>
       <c r="R27" t="n">
-        <v>6955759</v>
+        <v>6955757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
         <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472095</v>
+        <v>129472097</v>
       </c>
       <c r="B29" t="n">
-        <v>97587</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628650</v>
+        <v>628701</v>
       </c>
       <c r="R29" t="n">
-        <v>6955757</v>
+        <v>6955786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>91968</v>
+        <v>91969</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,50 +3662,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R31" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3737,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3871,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3882,34 +3877,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R33" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,6 +3942,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,7 +4008,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R34" t="n">
         <v>6955801</v>
@@ -4039,11 +4044,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R37" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>91763</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,34 +4683,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R41" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4745,17 +4748,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4774,48 +4773,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129473075</v>
+        <v>129472084</v>
       </c>
       <c r="B42" t="n">
-        <v>91762</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628595</v>
+        <v>628556</v>
       </c>
       <c r="R42" t="n">
-        <v>6955801</v>
+        <v>6955608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,13 +4846,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R43" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472069</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628725</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955752</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
         <v>129472073</v>
       </c>
       <c r="B49" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472069</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628725</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955752</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472103</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628614</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955785</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472086</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628666</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955777</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B22" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R22" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,6 +2856,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472089</v>
+        <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628636</v>
+        <v>628701</v>
       </c>
       <c r="R25" t="n">
-        <v>6955724</v>
+        <v>6955786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472091</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
         <v>91848</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628624</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955759</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472095</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>97595</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628650</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955757</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472097</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>97595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628701</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955786</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,32 +3662,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
         <v>6955801</v>
@@ -3733,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3764,7 +3759,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472075</v>
+        <v>129464211</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3793,16 +3788,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628611</v>
+        <v>628639</v>
       </c>
       <c r="R32" t="n">
-        <v>6955783</v>
+        <v>6955882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,7 +3866,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3895,21 +3895,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3941,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,32 +3968,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472067</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4008,7 +4003,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628597</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
         <v>6955801</v>
@@ -4044,6 +4039,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R35" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R37" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5375,7 +5375,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472069</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
         <v>91550</v>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628725</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955752</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472073</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
         <v>91550</v>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628698</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955800</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472072</v>
+        <v>129472086</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628696</v>
+        <v>628666</v>
       </c>
       <c r="R14" t="n">
-        <v>6955790</v>
+        <v>6955777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,6 +2060,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472086</v>
+        <v>129472072</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628666</v>
+        <v>628696</v>
       </c>
       <c r="R16" t="n">
-        <v>6955777</v>
+        <v>6955790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472068</v>
+        <v>129472094</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628531</v>
+        <v>628694</v>
       </c>
       <c r="R21" t="n">
-        <v>6955789</v>
+        <v>6955797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R23" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472097</v>
+        <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628701</v>
+        <v>628636</v>
       </c>
       <c r="R25" t="n">
-        <v>6955786</v>
+        <v>6955724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472091</v>
       </c>
       <c r="B26" t="n">
         <v>91848</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628624</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472091</v>
+        <v>129472065</v>
       </c>
       <c r="B27" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628624</v>
+        <v>628619</v>
       </c>
       <c r="R27" t="n">
-        <v>6955759</v>
+        <v>6955754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472097</v>
       </c>
       <c r="B28" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628701</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472067</v>
+        <v>129472075</v>
       </c>
       <c r="B31" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628597</v>
+        <v>628611</v>
       </c>
       <c r="R31" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,6 +3733,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,50 +3764,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R32" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472075</v>
+        <v>129472067</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628611</v>
+        <v>628597</v>
       </c>
       <c r="R33" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,11 +3937,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,45 +3963,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129473075</v>
+        <v>129472105</v>
       </c>
       <c r="B41" t="n">
-        <v>91763</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,37 +4683,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628595</v>
+        <v>628512</v>
       </c>
       <c r="R41" t="n">
-        <v>6955801</v>
+        <v>6955747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,13 +4745,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4875,10 +4876,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B43" t="n">
-        <v>98724</v>
+        <v>91763</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,34 +4887,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R43" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,17 +4952,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472086</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628666</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955777</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2060,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472072</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628696</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955790</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
         <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472094</v>
+        <v>129472079</v>
       </c>
       <c r="B21" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628694</v>
+        <v>628550</v>
       </c>
       <c r="R21" t="n">
-        <v>6955797</v>
+        <v>6955726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R22" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,11 +2861,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472068</v>
+        <v>129472094</v>
       </c>
       <c r="B23" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628531</v>
+        <v>628694</v>
       </c>
       <c r="R23" t="n">
-        <v>6955789</v>
+        <v>6955797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R25" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472091</v>
+        <v>129472097</v>
       </c>
       <c r="B26" t="n">
-        <v>91848</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628624</v>
+        <v>628701</v>
       </c>
       <c r="R26" t="n">
-        <v>6955759</v>
+        <v>6955786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472065</v>
+        <v>129472095</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>97598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628619</v>
+        <v>628650</v>
       </c>
       <c r="R27" t="n">
-        <v>6955754</v>
+        <v>6955757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472097</v>
+        <v>129472089</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628701</v>
+        <v>628636</v>
       </c>
       <c r="R28" t="n">
-        <v>6955786</v>
+        <v>6955724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472095</v>
+        <v>129472091</v>
       </c>
       <c r="B29" t="n">
-        <v>97595</v>
+        <v>91851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628650</v>
+        <v>628624</v>
       </c>
       <c r="R29" t="n">
-        <v>6955757</v>
+        <v>6955759</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>91969</v>
+        <v>91972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472075</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628611</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3764,45 +3759,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R32" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472067</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628597</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,6 +3937,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,50 +3968,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>91766</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,34 +4683,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R41" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4745,17 +4748,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4876,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129473075</v>
+        <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>91763</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4887,37 +4886,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628595</v>
+        <v>628512</v>
       </c>
       <c r="R43" t="n">
-        <v>6955801</v>
+        <v>6955747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,13 +4948,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>129472069</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R50" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5640,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5666,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R51" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472072</v>
+        <v>129472103</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628696</v>
+        <v>628614</v>
       </c>
       <c r="R14" t="n">
-        <v>6955790</v>
+        <v>6955785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,6 +2060,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R15" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472086</v>
+        <v>129472100</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628666</v>
+        <v>628692</v>
       </c>
       <c r="R16" t="n">
-        <v>6955777</v>
+        <v>6955809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472103</v>
+        <v>129472086</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628614</v>
+        <v>628666</v>
       </c>
       <c r="R17" t="n">
-        <v>6955785</v>
+        <v>6955777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472065</v>
+        <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628619</v>
+        <v>628636</v>
       </c>
       <c r="R25" t="n">
-        <v>6955754</v>
+        <v>6955724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472097</v>
+        <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628701</v>
+        <v>628624</v>
       </c>
       <c r="R26" t="n">
-        <v>6955786</v>
+        <v>6955759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472095</v>
+        <v>129472065</v>
       </c>
       <c r="B27" t="n">
-        <v>97598</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628650</v>
+        <v>628619</v>
       </c>
       <c r="R27" t="n">
-        <v>6955757</v>
+        <v>6955754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472089</v>
+        <v>129472097</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628636</v>
+        <v>628701</v>
       </c>
       <c r="R28" t="n">
-        <v>6955724</v>
+        <v>6955786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472091</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>91851</v>
+        <v>97598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628624</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955759</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3759,50 +3759,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R32" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3968,45 +3963,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R37" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R39" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,32 +4575,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R40" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,11 +5640,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5671,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R51" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472103</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628614</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955785</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2060,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472100</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628692</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955809</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472086</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628666</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955777</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472068</v>
+        <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628531</v>
+        <v>628694</v>
       </c>
       <c r="R22" t="n">
-        <v>6955789</v>
+        <v>6955797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472094</v>
+        <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628694</v>
+        <v>628550</v>
       </c>
       <c r="R23" t="n">
-        <v>6955797</v>
+        <v>6955726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2953,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3759,45 +3759,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R32" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3834,7 +3839,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3963,50 +3968,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R35" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R37" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R39" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,32 +4570,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R40" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R14" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R15" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R21" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R23" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,11 +2958,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472089</v>
+        <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628636</v>
+        <v>628701</v>
       </c>
       <c r="R25" t="n">
-        <v>6955724</v>
+        <v>6955786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472065</v>
+        <v>129472089</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628619</v>
+        <v>628636</v>
       </c>
       <c r="R27" t="n">
-        <v>6955754</v>
+        <v>6955724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472097</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628701</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955786</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,34 +3673,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R31" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,6 +3738,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,7 +3769,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3788,21 +3798,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R32" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3844,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,32 +3871,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R33" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3946,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,7 +4008,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R34" t="n">
         <v>6955801</v>
@@ -4039,11 +4044,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472073</v>
+        <v>129472108</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628698</v>
+        <v>628517</v>
       </c>
       <c r="R48" t="n">
-        <v>6955800</v>
+        <v>6955756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472069</v>
+        <v>129472073</v>
       </c>
       <c r="B49" t="n">
         <v>91553</v>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628725</v>
+        <v>628698</v>
       </c>
       <c r="R49" t="n">
-        <v>6955752</v>
+        <v>6955800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472108</v>
+        <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628517</v>
+        <v>628725</v>
       </c>
       <c r="R50" t="n">
-        <v>6955756</v>
+        <v>6955752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R23" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2953,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472091</v>
+        <v>129472095</v>
       </c>
       <c r="B26" t="n">
-        <v>91851</v>
+        <v>97598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628624</v>
+        <v>628650</v>
       </c>
       <c r="R26" t="n">
-        <v>6955759</v>
+        <v>6955757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472091</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472095</v>
+        <v>129472065</v>
       </c>
       <c r="B29" t="n">
-        <v>97598</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628650</v>
+        <v>628619</v>
       </c>
       <c r="R29" t="n">
-        <v>6955757</v>
+        <v>6955754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464211</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,39 +3673,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628639</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3871,45 +3861,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R33" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3941,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,32 +3968,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472067</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4008,7 +4003,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628597</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
         <v>6955801</v>
@@ -4044,6 +4039,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R37" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472073</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
         <v>91553</v>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628698</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955800</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472069</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628725</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955752</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472100</v>
+        <v>129472086</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628692</v>
+        <v>628666</v>
       </c>
       <c r="R15" t="n">
-        <v>6955809</v>
+        <v>6955777</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2188,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472086</v>
+        <v>129472103</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628666</v>
+        <v>628614</v>
       </c>
       <c r="R16" t="n">
-        <v>6955777</v>
+        <v>6955785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472103</v>
+        <v>129472100</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628614</v>
+        <v>628692</v>
       </c>
       <c r="R17" t="n">
-        <v>6955785</v>
+        <v>6955809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472095</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
-        <v>97598</v>
+        <v>91851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628650</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955757</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472089</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
         <v>91851</v>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628636</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955724</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472091</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955759</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472065</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>97598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628619</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955754</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3759,32 +3759,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R32" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3968,32 +3968,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129472075</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628611</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R35" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R37" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,32 +4773,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R42" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472105</v>
+        <v>129472084</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628512</v>
+        <v>628556</v>
       </c>
       <c r="R43" t="n">
-        <v>6955747</v>
+        <v>6955608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472073</v>
+        <v>129472108</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628698</v>
+        <v>628517</v>
       </c>
       <c r="R48" t="n">
-        <v>6955800</v>
+        <v>6955756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472069</v>
+        <v>129472073</v>
       </c>
       <c r="B49" t="n">
         <v>91553</v>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628725</v>
+        <v>628698</v>
       </c>
       <c r="R49" t="n">
-        <v>6955752</v>
+        <v>6955800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472108</v>
+        <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628517</v>
+        <v>628725</v>
       </c>
       <c r="R50" t="n">
-        <v>6955756</v>
+        <v>6955752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>129472086</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,32 +2188,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472103</v>
+        <v>129472100</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628614</v>
+        <v>628692</v>
       </c>
       <c r="R16" t="n">
-        <v>6955785</v>
+        <v>6955809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472100</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628692</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955809</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129464348</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129472096</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R21" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,7 +2793,7 @@
         <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R23" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,11 +2958,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,32 +3081,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472097</v>
+        <v>129472095</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>97627</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628701</v>
+        <v>628650</v>
       </c>
       <c r="R25" t="n">
-        <v>6955786</v>
+        <v>6955757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B26" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472091</v>
+        <v>129472097</v>
       </c>
       <c r="B27" t="n">
-        <v>91851</v>
+        <v>80175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628624</v>
+        <v>628701</v>
       </c>
       <c r="R27" t="n">
-        <v>6955759</v>
+        <v>6955786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472091</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472095</v>
+        <v>129472089</v>
       </c>
       <c r="B29" t="n">
-        <v>97598</v>
+        <v>91879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628650</v>
+        <v>628636</v>
       </c>
       <c r="R29" t="n">
-        <v>6955757</v>
+        <v>6955724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>91972</v>
+        <v>92000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,32 +3662,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472067</v>
+        <v>129472106</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628597</v>
+        <v>628696</v>
       </c>
       <c r="R31" t="n">
         <v>6955801</v>
@@ -3733,6 +3733,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,32 +3764,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3794,7 +3799,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R32" t="n">
         <v>6955801</v>
@@ -3830,11 +3835,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,7 +3864,7 @@
         <v>129464211</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>129472075</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>129472083</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129472080</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>129472085</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R39" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,32 +4575,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R40" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4675,7 +4675,7 @@
         <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>91766</v>
+        <v>91794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472105</v>
+        <v>129472084</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628512</v>
+        <v>628556</v>
       </c>
       <c r="R42" t="n">
-        <v>6955747</v>
+        <v>6955608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R43" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4980,7 +4980,7 @@
         <v>129472109</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>129472077</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>129472076</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472073</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628698</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955800</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472069</v>
+        <v>129472082</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628725</v>
+        <v>628544</v>
       </c>
       <c r="R50" t="n">
-        <v>6955752</v>
+        <v>6955659</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5640,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5666,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R51" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R14" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472086</v>
+        <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>91581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628666</v>
+        <v>628696</v>
       </c>
       <c r="R15" t="n">
-        <v>6955777</v>
+        <v>6955790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,11 +2157,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472100</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628692</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955809</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472079</v>
+        <v>129472094</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>91879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628550</v>
+        <v>628694</v>
       </c>
       <c r="R21" t="n">
-        <v>6955726</v>
+        <v>6955797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>91581</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R22" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>91581</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R23" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2953,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R39" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,32 +4570,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R40" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472100</v>
+        <v>129472086</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628692</v>
+        <v>628666</v>
       </c>
       <c r="R14" t="n">
-        <v>6955809</v>
+        <v>6955777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,6 +2060,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,32 +2091,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472103</v>
       </c>
       <c r="B15" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628614</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,6 +2162,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472086</v>
+        <v>129472100</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628666</v>
+        <v>628692</v>
       </c>
       <c r="R16" t="n">
-        <v>6955777</v>
+        <v>6955809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2264,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472103</v>
+        <v>129472072</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628614</v>
+        <v>628696</v>
       </c>
       <c r="R17" t="n">
-        <v>6955785</v>
+        <v>6955790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129464348</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129472096</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129472094</v>
       </c>
       <c r="B21" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129472095</v>
       </c>
       <c r="B25" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472065</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628619</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955754</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472097</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>80175</v>
+        <v>91885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628701</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955786</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472091</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955759</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472089</v>
+        <v>129472097</v>
       </c>
       <c r="B29" t="n">
-        <v>91879</v>
+        <v>80180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628636</v>
+        <v>628701</v>
       </c>
       <c r="R29" t="n">
-        <v>6955724</v>
+        <v>6955786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>92000</v>
+        <v>92006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,32 +3662,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
         <v>6955801</v>
@@ -3733,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3764,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B32" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,34 +3770,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R32" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,6 +3835,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3890,21 +3895,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,32 +3968,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4073,7 +4073,7 @@
         <v>129472083</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129472080</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>129472085</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>91794</v>
+        <v>91800</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>129472084</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>129472109</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>129472077</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>129472076</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472073</v>
+        <v>129472082</v>
       </c>
       <c r="B48" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628698</v>
+        <v>628544</v>
       </c>
       <c r="R48" t="n">
-        <v>6955800</v>
+        <v>6955659</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,6 +5446,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5472,10 +5477,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472069</v>
+        <v>129472073</v>
       </c>
       <c r="B49" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628725</v>
+        <v>628698</v>
       </c>
       <c r="R49" t="n">
-        <v>6955752</v>
+        <v>6955800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472082</v>
+        <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5585,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628544</v>
+        <v>628725</v>
       </c>
       <c r="R50" t="n">
-        <v>6955659</v>
+        <v>6955752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,11 +5645,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5674,7 +5674,7 @@
         <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>129472086</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,32 +2091,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472103</v>
+        <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628614</v>
+        <v>628696</v>
       </c>
       <c r="R15" t="n">
-        <v>6955785</v>
+        <v>6955790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,11 +2162,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,7 +2191,7 @@
         <v>129472100</v>
       </c>
       <c r="B16" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472072</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628696</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955790</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129464348</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129472096</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129472094</v>
       </c>
       <c r="B21" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,32 +3081,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472095</v>
+        <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>97639</v>
+        <v>80181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628650</v>
+        <v>628701</v>
       </c>
       <c r="R25" t="n">
-        <v>6955757</v>
+        <v>6955786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472095</v>
       </c>
       <c r="B26" t="n">
-        <v>91885</v>
+        <v>97640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628650</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472089</v>
       </c>
       <c r="B28" t="n">
-        <v>91587</v>
+        <v>91886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628636</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472097</v>
+        <v>129472065</v>
       </c>
       <c r="B29" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628701</v>
+        <v>628619</v>
       </c>
       <c r="R29" t="n">
-        <v>6955786</v>
+        <v>6955754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>92006</v>
+        <v>92007</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>129464211</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>129472075</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>129472083</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129472080</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>129472085</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B39" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R39" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,32 +4575,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R40" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4675,7 +4675,7 @@
         <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>91800</v>
+        <v>91801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>129472084</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>129472109</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>129472077</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>129472076</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>129472082</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>129472073</v>
       </c>
       <c r="B49" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472095</v>
+        <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>97640</v>
+        <v>91886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628650</v>
+        <v>628624</v>
       </c>
       <c r="R26" t="n">
-        <v>6955757</v>
+        <v>6955759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472091</v>
+        <v>129472089</v>
       </c>
       <c r="B27" t="n">
         <v>91886</v>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628624</v>
+        <v>628636</v>
       </c>
       <c r="R27" t="n">
-        <v>6955759</v>
+        <v>6955724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>91886</v>
+        <v>91588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472065</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>97640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628619</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955754</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472086</v>
+        <v>129472100</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628666</v>
+        <v>628692</v>
       </c>
       <c r="R14" t="n">
-        <v>6955777</v>
+        <v>6955809</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2060,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,7 +2089,7 @@
         <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472100</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628692</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955809</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
         <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129472096</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>91886</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472068</v>
+        <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>91588</v>
+        <v>91891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628531</v>
+        <v>628694</v>
       </c>
       <c r="R22" t="n">
-        <v>6955789</v>
+        <v>6955797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472097</v>
+        <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628701</v>
+        <v>628636</v>
       </c>
       <c r="R25" t="n">
-        <v>6955786</v>
+        <v>6955724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
         <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B27" t="n">
-        <v>91886</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R27" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472065</v>
+        <v>129472097</v>
       </c>
       <c r="B28" t="n">
-        <v>91588</v>
+        <v>80186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628619</v>
+        <v>628701</v>
       </c>
       <c r="R28" t="n">
-        <v>6955754</v>
+        <v>6955786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>92007</v>
+        <v>92012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3788,21 +3788,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R32" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,7 +3861,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472075</v>
+        <v>129464211</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -3895,16 +3890,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628611</v>
+        <v>628639</v>
       </c>
       <c r="R33" t="n">
-        <v>6955783</v>
+        <v>6955882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,7 +3971,7 @@
         <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R37" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R39" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,32 +4570,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R40" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129473075</v>
+        <v>129472105</v>
       </c>
       <c r="B41" t="n">
-        <v>91801</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,37 +4683,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628595</v>
+        <v>628512</v>
       </c>
       <c r="R41" t="n">
-        <v>6955801</v>
+        <v>6955747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,13 +4745,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4773,45 +4774,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472084</v>
+        <v>129473075</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>91806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628556</v>
+        <v>628595</v>
       </c>
       <c r="R42" t="n">
-        <v>6955608</v>
+        <v>6955801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4846,17 +4850,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472105</v>
+        <v>129472084</v>
       </c>
       <c r="B43" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628512</v>
+        <v>628556</v>
       </c>
       <c r="R43" t="n">
-        <v>6955747</v>
+        <v>6955608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4980,7 +4980,7 @@
         <v>129472109</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R48" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,11 +5446,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5477,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472073</v>
+        <v>129472082</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5488,21 +5483,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628698</v>
+        <v>628544</v>
       </c>
       <c r="R49" t="n">
-        <v>6955800</v>
+        <v>6955659</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5548,6 +5543,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5577,7 +5577,7 @@
         <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5671,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472108</v>
+        <v>129472073</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628517</v>
+        <v>628698</v>
       </c>
       <c r="R51" t="n">
-        <v>6955756</v>
+        <v>6955800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,34 +3673,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R31" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,6 +3738,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3861,10 +3871,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129464211</v>
+        <v>129472067</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,39 +3882,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628639</v>
+        <v>628597</v>
       </c>
       <c r="R33" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,11 +3942,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472085</v>
+        <v>129472083</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628557</v>
+        <v>628567</v>
       </c>
       <c r="R35" t="n">
-        <v>6955601</v>
+        <v>6955620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R37" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4672,32 +4672,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472105</v>
+        <v>129472084</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628512</v>
+        <v>628556</v>
       </c>
       <c r="R41" t="n">
-        <v>6955747</v>
+        <v>6955608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129473075</v>
+        <v>129472105</v>
       </c>
       <c r="B42" t="n">
-        <v>91806</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4785,37 +4785,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628595</v>
+        <v>628512</v>
       </c>
       <c r="R42" t="n">
-        <v>6955801</v>
+        <v>6955747</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,13 +4847,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>14 ex</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4875,45 +4876,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472084</v>
+        <v>129473075</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>91806</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628556</v>
+        <v>628595</v>
       </c>
       <c r="R43" t="n">
-        <v>6955608</v>
+        <v>6955801</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,17 +4952,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472082</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5483,21 +5483,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628544</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955659</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,11 +5543,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5574,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472069</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628725</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955752</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472073</v>
+        <v>129472082</v>
       </c>
       <c r="B51" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628698</v>
+        <v>628544</v>
       </c>
       <c r="R51" t="n">
-        <v>6955800</v>
+        <v>6955659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472072</v>
+        <v>129472100</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628696</v>
+        <v>628692</v>
       </c>
       <c r="R14" t="n">
-        <v>6955790</v>
+        <v>6955809</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R15" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R25" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472091</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
         <v>91891</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628624</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955759</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472065</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628619</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955754</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464211</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,39 +3673,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628639</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3769,7 +3759,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472075</v>
+        <v>129464211</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3798,16 +3788,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628611</v>
+        <v>628639</v>
       </c>
       <c r="R32" t="n">
-        <v>6955783</v>
+        <v>6955882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3839,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3871,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472067</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3882,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3906,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628597</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,6 +3937,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R39" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4570,32 +4575,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R40" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4672,32 +4672,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R41" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>91806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4785,34 +4785,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R42" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,17 +4850,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4876,48 +4875,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129473075</v>
+        <v>129472084</v>
       </c>
       <c r="B43" t="n">
-        <v>91806</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628595</v>
+        <v>628556</v>
       </c>
       <c r="R43" t="n">
-        <v>6955801</v>
+        <v>6955608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,13 +4948,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5569,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R50" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,6 +5640,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5666,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R51" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -2086,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472072</v>
+        <v>129472103</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628696</v>
+        <v>628614</v>
       </c>
       <c r="R15" t="n">
-        <v>6955790</v>
+        <v>6955785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472086</v>
+        <v>129472072</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628666</v>
+        <v>628696</v>
       </c>
       <c r="R16" t="n">
-        <v>6955777</v>
+        <v>6955790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472103</v>
+        <v>129472086</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628614</v>
+        <v>628666</v>
       </c>
       <c r="R17" t="n">
-        <v>6955785</v>
+        <v>6955777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472065</v>
+        <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628619</v>
+        <v>628701</v>
       </c>
       <c r="R25" t="n">
-        <v>6955754</v>
+        <v>6955786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472089</v>
+        <v>129472095</v>
       </c>
       <c r="B26" t="n">
-        <v>91891</v>
+        <v>97645</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628636</v>
+        <v>628650</v>
       </c>
       <c r="R26" t="n">
-        <v>6955724</v>
+        <v>6955757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472091</v>
+        <v>129472089</v>
       </c>
       <c r="B27" t="n">
         <v>91891</v>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628624</v>
+        <v>628636</v>
       </c>
       <c r="R27" t="n">
-        <v>6955759</v>
+        <v>6955724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472097</v>
+        <v>129472091</v>
       </c>
       <c r="B28" t="n">
-        <v>80186</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628701</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6955786</v>
+        <v>6955759</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472095</v>
+        <v>129472065</v>
       </c>
       <c r="B29" t="n">
-        <v>97645</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628650</v>
+        <v>628619</v>
       </c>
       <c r="R29" t="n">
-        <v>6955757</v>
+        <v>6955754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129472102</v>
+        <v>129472099</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628568</v>
+        <v>628699</v>
       </c>
       <c r="R39" t="n">
-        <v>6955839</v>
+        <v>6955804</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,32 +4570,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129472099</v>
+        <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628699</v>
+        <v>628568</v>
       </c>
       <c r="R40" t="n">
-        <v>6955804</v>
+        <v>6955839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129472105</v>
+        <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>91806</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,34 +4683,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyrberget, Ång</t>
+          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628512</v>
+        <v>628595</v>
       </c>
       <c r="R41" t="n">
-        <v>6955747</v>
+        <v>6955801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4745,17 +4748,13 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>14 ex</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4774,48 +4773,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129473075</v>
+        <v>129472084</v>
       </c>
       <c r="B42" t="n">
-        <v>91806</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyrberget, Södergård, Gussjön, Ång</t>
+          <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628595</v>
+        <v>628556</v>
       </c>
       <c r="R42" t="n">
-        <v>6955801</v>
+        <v>6955608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,13 +4846,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129472084</v>
+        <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628556</v>
+        <v>628512</v>
       </c>
       <c r="R43" t="n">
-        <v>6955608</v>
+        <v>6955747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472073</v>
+        <v>129472108</v>
       </c>
       <c r="B48" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628698</v>
+        <v>628517</v>
       </c>
       <c r="R48" t="n">
-        <v>6955800</v>
+        <v>6955756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472069</v>
+        <v>129472082</v>
       </c>
       <c r="B49" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5483,21 +5483,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628725</v>
+        <v>628544</v>
       </c>
       <c r="R49" t="n">
-        <v>6955752</v>
+        <v>6955659</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,6 +5543,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5569,10 +5574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472082</v>
+        <v>129472073</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5585,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628544</v>
+        <v>628698</v>
       </c>
       <c r="R50" t="n">
-        <v>6955659</v>
+        <v>6955800</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,11 +5645,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5671,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472108</v>
+        <v>129472069</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628517</v>
+        <v>628725</v>
       </c>
       <c r="R51" t="n">
-        <v>6955756</v>
+        <v>6955752</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129472100</v>
+        <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628692</v>
+        <v>628696</v>
       </c>
       <c r="R14" t="n">
-        <v>6955809</v>
+        <v>6955790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129472103</v>
+        <v>129472100</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628614</v>
+        <v>628692</v>
       </c>
       <c r="R15" t="n">
-        <v>6955785</v>
+        <v>6955809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,11 +2157,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>200 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129472072</v>
+        <v>129472086</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628696</v>
+        <v>628666</v>
       </c>
       <c r="R16" t="n">
-        <v>6955790</v>
+        <v>6955777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela trädet är fullt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129472086</v>
+        <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628666</v>
+        <v>628614</v>
       </c>
       <c r="R17" t="n">
-        <v>6955777</v>
+        <v>6955785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela trädet är fullt</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472068</v>
+        <v>129472079</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628531</v>
+        <v>628550</v>
       </c>
       <c r="R21" t="n">
-        <v>6955789</v>
+        <v>6955726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472094</v>
+        <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91891</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628694</v>
+        <v>628531</v>
       </c>
       <c r="R22" t="n">
-        <v>6955797</v>
+        <v>6955789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472079</v>
+        <v>129472094</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>91895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628550</v>
+        <v>628694</v>
       </c>
       <c r="R23" t="n">
-        <v>6955726</v>
+        <v>6955797</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,11 +2958,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472097</v>
+        <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>80186</v>
+        <v>91895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628701</v>
+        <v>628636</v>
       </c>
       <c r="R25" t="n">
-        <v>6955786</v>
+        <v>6955724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472095</v>
+        <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>97645</v>
+        <v>91895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628650</v>
+        <v>628624</v>
       </c>
       <c r="R26" t="n">
-        <v>6955757</v>
+        <v>6955759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472089</v>
+        <v>129472065</v>
       </c>
       <c r="B27" t="n">
-        <v>91891</v>
+        <v>91597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628636</v>
+        <v>628619</v>
       </c>
       <c r="R27" t="n">
-        <v>6955724</v>
+        <v>6955754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472091</v>
+        <v>129472097</v>
       </c>
       <c r="B28" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628701</v>
       </c>
       <c r="R28" t="n">
-        <v>6955759</v>
+        <v>6955786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129472065</v>
+        <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>97649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628619</v>
+        <v>628650</v>
       </c>
       <c r="R29" t="n">
-        <v>6955754</v>
+        <v>6955757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>92012</v>
+        <v>92016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,34 +3673,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R31" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,6 +3738,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,7 +3769,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3788,21 +3798,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R32" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3844,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,32 +3871,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R33" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3946,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129472067</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,7 +4008,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628597</v>
       </c>
       <c r="R34" t="n">
         <v>6955801</v>
@@ -4039,11 +4044,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>91806</v>
+        <v>91810</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472108</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628517</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955756</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472082</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5483,21 +5483,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628544</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955659</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,11 +5543,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5574,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472073</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628698</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955800</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472069</v>
+        <v>129472082</v>
       </c>
       <c r="B51" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628725</v>
+        <v>628544</v>
       </c>
       <c r="R51" t="n">
-        <v>6955752</v>
+        <v>6955659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -1992,7 +1992,7 @@
         <v>129472072</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129472103</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129472088</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>129472068</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129472094</v>
       </c>
       <c r="B23" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129472092</v>
       </c>
       <c r="B24" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129472089</v>
       </c>
       <c r="B25" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129472091</v>
       </c>
       <c r="B26" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>129472065</v>
       </c>
       <c r="B27" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129472095</v>
       </c>
       <c r="B29" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>129472101</v>
       </c>
       <c r="B30" t="n">
-        <v>92016</v>
+        <v>92018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129464211</v>
+        <v>129472067</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,39 +3673,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628639</v>
+        <v>628597</v>
       </c>
       <c r="R31" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,11 +3733,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3769,32 +3759,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3804,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R32" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3871,32 +3861,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472106</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3906,10 +3896,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628696</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3936,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472067</v>
+        <v>129464211</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,34 +3974,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628597</v>
+        <v>628639</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,7 +4172,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472080</v>
+        <v>129472085</v>
       </c>
       <c r="B36" t="n">
         <v>57736</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628556</v>
+        <v>628557</v>
       </c>
       <c r="R36" t="n">
-        <v>6955681</v>
+        <v>6955601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472085</v>
+        <v>129472080</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628557</v>
+        <v>628556</v>
       </c>
       <c r="R37" t="n">
-        <v>6955601</v>
+        <v>6955681</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>129472066</v>
       </c>
       <c r="B38" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129472102</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>129473075</v>
       </c>
       <c r="B41" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129472105</v>
       </c>
       <c r="B43" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>129472087</v>
       </c>
       <c r="B45" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>129472069</v>
       </c>
       <c r="B49" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -3759,32 +3759,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472106</v>
+        <v>129472075</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628696</v>
+        <v>628611</v>
       </c>
       <c r="R32" t="n">
-        <v>6955801</v>
+        <v>6955783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129472075</v>
+        <v>129464211</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -3890,16 +3890,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628611</v>
+        <v>628639</v>
       </c>
       <c r="R33" t="n">
-        <v>6955783</v>
+        <v>6955882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,7 +3941,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,50 +3968,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129464211</v>
+        <v>129472106</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628639</v>
+        <v>628696</v>
       </c>
       <c r="R34" t="n">
-        <v>6955882</v>
+        <v>6955801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129472083</v>
+        <v>129472085</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628567</v>
+        <v>628557</v>
       </c>
       <c r="R35" t="n">
-        <v>6955620</v>
+        <v>6955601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4172,7 +4172,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129472085</v>
+        <v>129472080</v>
       </c>
       <c r="B36" t="n">
         <v>57736</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628557</v>
+        <v>628556</v>
       </c>
       <c r="R36" t="n">
-        <v>6955601</v>
+        <v>6955681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129472080</v>
+        <v>129472083</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628556</v>
+        <v>628567</v>
       </c>
       <c r="R37" t="n">
-        <v>6955681</v>
+        <v>6955620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472073</v>
+        <v>129472082</v>
       </c>
       <c r="B48" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628698</v>
+        <v>628544</v>
       </c>
       <c r="R48" t="n">
-        <v>6955800</v>
+        <v>6955659</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,6 +5446,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5472,7 +5477,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472069</v>
+        <v>129472073</v>
       </c>
       <c r="B49" t="n">
         <v>91599</v>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628725</v>
+        <v>628698</v>
       </c>
       <c r="R49" t="n">
-        <v>6955752</v>
+        <v>6955800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,10 +5574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472108</v>
+        <v>129472069</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,21 +5585,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628517</v>
+        <v>628725</v>
       </c>
       <c r="R50" t="n">
-        <v>6955756</v>
+        <v>6955752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5666,10 +5671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472082</v>
+        <v>129472108</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5682,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628544</v>
+        <v>628517</v>
       </c>
       <c r="R51" t="n">
-        <v>6955659</v>
+        <v>6955756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129472079</v>
+        <v>129472068</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628550</v>
+        <v>628531</v>
       </c>
       <c r="R21" t="n">
-        <v>6955726</v>
+        <v>6955789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129472068</v>
+        <v>129472094</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628531</v>
+        <v>628694</v>
       </c>
       <c r="R22" t="n">
-        <v>6955789</v>
+        <v>6955797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129472094</v>
+        <v>129472079</v>
       </c>
       <c r="B23" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628694</v>
+        <v>628550</v>
       </c>
       <c r="R23" t="n">
-        <v>6955797</v>
+        <v>6955726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2953,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129472089</v>
+        <v>129472097</v>
       </c>
       <c r="B25" t="n">
-        <v>91897</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628636</v>
+        <v>628701</v>
       </c>
       <c r="R25" t="n">
-        <v>6955724</v>
+        <v>6955786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129472091</v>
+        <v>129472089</v>
       </c>
       <c r="B26" t="n">
         <v>91897</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628624</v>
+        <v>628636</v>
       </c>
       <c r="R26" t="n">
-        <v>6955759</v>
+        <v>6955724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129472065</v>
+        <v>129472091</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628619</v>
+        <v>628624</v>
       </c>
       <c r="R27" t="n">
-        <v>6955754</v>
+        <v>6955759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129472097</v>
+        <v>129472065</v>
       </c>
       <c r="B28" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628701</v>
+        <v>628619</v>
       </c>
       <c r="R28" t="n">
-        <v>6955786</v>
+        <v>6955754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,32 +3759,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129472075</v>
+        <v>129472106</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628611</v>
+        <v>628696</v>
       </c>
       <c r="R32" t="n">
-        <v>6955783</v>
+        <v>6955801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129464211</v>
+        <v>129472075</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -3890,21 +3890,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628639</v>
+        <v>628611</v>
       </c>
       <c r="R33" t="n">
-        <v>6955882</v>
+        <v>6955783</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3936,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3968,45 +3963,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129472106</v>
+        <v>129464211</v>
       </c>
       <c r="B34" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628696</v>
+        <v>628639</v>
       </c>
       <c r="R34" t="n">
-        <v>6955801</v>
+        <v>6955882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -5375,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129472082</v>
+        <v>129472073</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628544</v>
+        <v>628698</v>
       </c>
       <c r="R48" t="n">
-        <v>6955659</v>
+        <v>6955800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,11 +5446,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5477,7 +5472,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129472073</v>
+        <v>129472069</v>
       </c>
       <c r="B49" t="n">
         <v>91599</v>
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628698</v>
+        <v>628725</v>
       </c>
       <c r="R49" t="n">
-        <v>6955800</v>
+        <v>6955752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5574,10 +5569,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129472069</v>
+        <v>129472108</v>
       </c>
       <c r="B50" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,21 +5580,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628725</v>
+        <v>628517</v>
       </c>
       <c r="R50" t="n">
-        <v>6955752</v>
+        <v>6955756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129472108</v>
+        <v>129472082</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628517</v>
+        <v>628544</v>
       </c>
       <c r="R51" t="n">
-        <v>6955756</v>
+        <v>6955659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49355-2025 artfynd.xlsx
+++ b/artfynd/A 49355-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129473075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54482673</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54482680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55948338</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901117</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472089</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472091</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472092</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271698</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55948337</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472065</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472066</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472067</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472068</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472069</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472072</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472073</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901118</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472087</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472088</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901104</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901112</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17269356</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3135,6 +3260,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901101</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3232,6 +3362,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901136</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3329,6 +3464,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472108</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3426,6 +3566,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472109</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3523,6 +3668,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901102</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3620,6 +3770,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54482607</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3717,6 +3872,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54482616</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3818,6 +3978,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55948339</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3915,6 +4080,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901115</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4012,6 +4182,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472096</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4109,6 +4284,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472097</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4206,6 +4386,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472099</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4303,6 +4488,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472100</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4410,6 +4600,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464211</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4517,6 +4712,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464348</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4619,6 +4819,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472075</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4721,6 +4926,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472076</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4823,6 +5033,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472077</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4925,6 +5140,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472079</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5027,6 +5247,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472080</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5129,6 +5354,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472082</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5231,6 +5461,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472083</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5333,6 +5568,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472084</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5435,6 +5675,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472085</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5537,6 +5782,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472086</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5634,6 +5884,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901103</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5731,6 +5986,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901116</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5828,6 +6088,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901119</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5930,6 +6195,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472102</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6032,6 +6302,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472103</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6134,6 +6409,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472105</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6236,6 +6516,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472106</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6333,6 +6618,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472095</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6430,6 +6720,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901114</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6531,8 +6826,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129472101</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>